--- a/resources/qa_test/formula_samples/_test_formula_nested.xlsx
+++ b/resources/qa_test/formula_samples/_test_formula_nested.xlsx
@@ -80,7 +80,7 @@
       <color theme="1"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -218,69 +218,11 @@
         <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -410,7 +352,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -461,24 +403,24 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>999</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="n">
         <f aca="false">C3+D3</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="n">
         <f aca="false">IF(E3=0,0,C3/E3)</f>
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="G3" s="1" t="n">
         <f aca="false">IF(E3=0,1,IF(C3/E3&gt;0.8,3,IF(C3/E3&gt;0.5,2,1)))</f>
@@ -487,24 +429,24 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1" t="n">
         <f aca="false">C4+D4</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="n">
         <f aca="false">IF(E4=0,0,C4/E4)</f>
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G4" s="1" t="n">
         <f aca="false">IF(E4=0,1,IF(C4/E4&gt;0.8,3,IF(C4/E4&gt;0.5,2,1)))</f>
@@ -513,20 +455,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="n">
         <f aca="false">C5+D5</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="n">
         <f aca="false">IF(E5=0,0,C5/E5)</f>
@@ -539,20 +481,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">C6+D6</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="n">
         <f aca="false">IF(E6=0,0,C6/E6)</f>
@@ -565,20 +507,20 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">C7+D7</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="n">
         <f aca="false">IF(E7=0,0,C7/E7)</f>
@@ -591,20 +533,20 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" s="1" t="n">
         <f aca="false">C8+D8</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="n">
         <f aca="false">IF(E8=0,0,C8/E8)</f>
@@ -617,20 +559,20 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="n">
         <f aca="false">C9+D9</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="n">
         <f aca="false">IF(E9=0,0,C9/E9)</f>
@@ -643,20 +585,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="n">
         <f aca="false">C10+D10</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="n">
         <f aca="false">IF(E10=0,0,C10/E10)</f>
@@ -669,20 +611,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="n">
         <f aca="false">C11+D11</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="n">
         <f aca="false">IF(E11=0,0,C11/E11)</f>
@@ -695,20 +637,20 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="n">
         <f aca="false">C12+D12</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="n">
         <f aca="false">IF(E12=0,0,C12/E12)</f>
@@ -721,20 +663,20 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
         <f aca="false">C13+D13</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="n">
         <f aca="false">IF(E13=0,0,C13/E13)</f>
@@ -747,20 +689,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="n">
         <f aca="false">C14+D14</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="n">
         <f aca="false">IF(E14=0,0,C14/E14)</f>
@@ -773,20 +715,20 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="n">
         <f aca="false">C15+D15</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1" t="n">
         <f aca="false">IF(E15=0,0,C15/E15)</f>
@@ -799,20 +741,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="n">
         <f aca="false">C16+D16</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F16" s="1" t="n">
         <f aca="false">IF(E16=0,0,C16/E16)</f>
@@ -825,20 +767,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>999</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1" t="n">
         <f aca="false">C17+D17</f>
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1" t="n">
         <f aca="false">IF(E17=0,0,C17/E17)</f>
@@ -847,6 +789,29 @@
       <c r="G17" s="1" t="n">
         <f aca="false">IF(E17=0,1,IF(C17/E17&gt;0.8,3,IF(C17/E17&gt;0.5,2,1)))</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/resources/qa_test/formula_samples/_test_formula_nested.xlsx
+++ b/resources/qa_test/formula_samples/_test_formula_nested.xlsx
@@ -86,16 +86,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -352,7 +355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -403,24 +406,24 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>2</v>
+        <v>999</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="n">
         <f aca="false">C3+D3</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1" t="n">
         <f aca="false">IF(E3=0,0,C3/E3)</f>
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G3" s="1" t="n">
         <f aca="false">IF(E3=0,1,IF(C3/E3&gt;0.8,3,IF(C3/E3&gt;0.5,2,1)))</f>
@@ -429,24 +432,24 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1" t="n">
         <f aca="false">C4+D4</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="n">
         <f aca="false">IF(E4=0,0,C4/E4)</f>
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="G4" s="1" t="n">
         <f aca="false">IF(E4=0,1,IF(C4/E4&gt;0.8,3,IF(C4/E4&gt;0.5,2,1)))</f>
@@ -455,20 +458,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1" t="n">
         <f aca="false">C5+D5</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="n">
         <f aca="false">IF(E5=0,0,C5/E5)</f>
@@ -481,20 +484,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">C6+D6</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="n">
         <f aca="false">IF(E6=0,0,C6/E6)</f>
@@ -507,20 +510,20 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">C7+D7</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="n">
         <f aca="false">IF(E7=0,0,C7/E7)</f>
@@ -533,20 +536,20 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="1" t="n">
         <f aca="false">C8+D8</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F8" s="1" t="n">
         <f aca="false">IF(E8=0,0,C8/E8)</f>
@@ -559,20 +562,20 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1" t="n">
         <f aca="false">C9+D9</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1" t="n">
         <f aca="false">IF(E9=0,0,C9/E9)</f>
@@ -585,20 +588,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="n">
         <f aca="false">C10+D10</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="n">
         <f aca="false">IF(E10=0,0,C10/E10)</f>
@@ -611,20 +614,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="n">
         <f aca="false">C11+D11</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="n">
         <f aca="false">IF(E11=0,0,C11/E11)</f>
@@ -637,20 +640,20 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="n">
         <f aca="false">C12+D12</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="n">
         <f aca="false">IF(E12=0,0,C12/E12)</f>
@@ -663,20 +666,20 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="n">
         <f aca="false">C13+D13</f>
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F13" s="1" t="n">
         <f aca="false">IF(E13=0,0,C13/E13)</f>
@@ -689,20 +692,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="n">
         <f aca="false">C14+D14</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1" t="n">
         <f aca="false">IF(E14=0,0,C14/E14)</f>
@@ -715,20 +718,20 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="n">
         <f aca="false">C15+D15</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="n">
         <f aca="false">IF(E15=0,0,C15/E15)</f>
@@ -741,20 +744,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="n">
         <f aca="false">C16+D16</f>
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="n">
         <f aca="false">IF(E16=0,0,C16/E16)</f>
@@ -767,20 +770,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="n">
         <f aca="false">C17+D17</f>
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="n">
         <f aca="false">IF(E17=0,0,C17/E17)</f>
@@ -789,29 +792,6 @@
       <c r="G17" s="1" t="n">
         <f aca="false">IF(E17=0,1,IF(C17/E17&gt;0.8,3,IF(C17/E17&gt;0.5,2,1)))</f>
         <v>2</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
